--- a/intermediate_data/LR_approved_summary.xlsx
+++ b/intermediate_data/LR_approved_summary.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6537837837837838</v>
+        <v>0.6814576271186441</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02057779285007733</v>
+        <v>0.02073715710883318</v>
       </c>
       <c r="E2" t="n">
-        <v>0.597972972972973</v>
+        <v>0.6338983050847458</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6993243243243243</v>
+        <v>0.7322033898305085</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6682934131736527</v>
+        <v>0.6548502994011975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01862382024282303</v>
+        <v>0.02008705755111195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6227544910179641</v>
+        <v>0.592814371257485</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7125748502994012</v>
+        <v>0.6976047904191617</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6662341772151898</v>
+        <v>0.6776265822784809</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02054048668114029</v>
+        <v>0.02022885140028705</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6044303797468354</v>
+        <v>0.6170886075949367</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7246835443037974</v>
+        <v>0.7215189873417721</v>
       </c>
     </row>
     <row r="5">
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6723509933774833</v>
+        <v>0.6524834437086092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01976345172526653</v>
+        <v>0.01995862350836525</v>
       </c>
       <c r="E5" t="n">
         <v>0.6092715231788079</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7086092715231788</v>
+        <v>0.7052980132450332</v>
       </c>
     </row>
     <row r="6">
@@ -553,16 +553,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6715131578947369</v>
+        <v>0.6963157894736841</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02145121670090113</v>
+        <v>0.0192142400989572</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6282894736842105</v>
+        <v>0.6513157894736842</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7203947368421053</v>
+        <v>0.7401315789473685</v>
       </c>
     </row>
     <row r="7">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6675</v>
+        <v>0.6479026217228465</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01843982933231113</v>
+        <v>0.02224691587136363</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6231343283582089</v>
+        <v>0.5917602996254682</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7052238805970149</v>
+        <v>0.700374531835206</v>
       </c>
     </row>
     <row r="8">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6923826714801443</v>
+        <v>0.6816666666666669</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02379395599206194</v>
+        <v>0.0242860934991898</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6462093862815884</v>
+        <v>0.6195652173913043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7436823104693141</v>
+        <v>0.7318840579710145</v>
       </c>
     </row>
     <row r="9">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6675092936802974</v>
+        <v>0.6552238805970149</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02467205018814955</v>
+        <v>0.02317210942568256</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6059479553903345</v>
+        <v>0.6119402985074627</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7360594795539034</v>
+        <v>0.7052238805970149</v>
       </c>
     </row>
     <row r="10">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6696000000000001</v>
+        <v>0.6759599999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02284068671684302</v>
+        <v>0.0216603347391055</v>
       </c>
       <c r="E10" t="n">
-        <v>0.596</v>
+        <v>0.604</v>
       </c>
       <c r="F10" t="n">
-        <v>0.76</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="11">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6732340425531913</v>
+        <v>0.6737446808510638</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02281796975316987</v>
+        <v>0.0255251441699454</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6127659574468085</v>
+        <v>0.5787234042553191</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7191489361702128</v>
+        <v>0.7446808510638298</v>
       </c>
     </row>
     <row r="12">
@@ -685,16 +685,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.683711790393013</v>
+        <v>0.690219298245614</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02621009791594747</v>
+        <v>0.02567032108958861</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6244541484716157</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7467248908296943</v>
+        <v>0.7543859649122807</v>
       </c>
     </row>
     <row r="13">
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6826222222222222</v>
+        <v>0.6795089285714284</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02901789377903731</v>
+        <v>0.02292470308012953</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6177777777777778</v>
+        <v>0.6116071428571429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7511111111111111</v>
+        <v>0.7366071428571429</v>
       </c>
     </row>
     <row r="14">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6660784313725492</v>
+        <v>0.6602950819672131</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02089883095320046</v>
+        <v>0.01949411646200951</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6241830065359477</v>
+        <v>0.6196721311475409</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7254901960784313</v>
+        <v>0.7049180327868853</v>
       </c>
     </row>
     <row r="15">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6521256038647344</v>
+        <v>0.6553398058252428</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02834816297489181</v>
+        <v>0.0228837146015064</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5797101449275363</v>
+        <v>0.6067961165048543</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7342995169082126</v>
+        <v>0.7184466019417476</v>
       </c>
     </row>
     <row r="16">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6633636363636363</v>
+        <v>0.6527397260273972</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02563021502440387</v>
+        <v>0.02447712134752807</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5844748858447488</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7181818181818181</v>
+        <v>0.7123287671232876</v>
       </c>
     </row>
     <row r="17">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7045</v>
+        <v>0.6868036529680366</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02542316542733428</v>
+        <v>0.02466329898942328</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6318181818181818</v>
+        <v>0.6118721461187214</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7681818181818182</v>
+        <v>0.7397260273972602</v>
       </c>
     </row>
     <row r="18">
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6715714285714287</v>
+        <v>0.6798086124401916</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0264781957224033</v>
+        <v>0.02574101771883541</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.6172248803827751</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="19">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6781944444444443</v>
+        <v>0.6995813953488371</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02767231976755799</v>
+        <v>0.02734613804018465</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6203703703703703</v>
+        <v>0.6372093023255814</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7453703703703703</v>
+        <v>0.7581395348837209</v>
       </c>
     </row>
     <row r="20">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6520588235294119</v>
+        <v>0.6613793103448274</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02591046355733168</v>
+        <v>0.02504620161935741</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5980392156862745</v>
+        <v>0.5911330049261084</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7205882352941176</v>
+        <v>0.7339901477832512</v>
       </c>
     </row>
     <row r="21">
@@ -883,16 +883,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6595336787564766</v>
+        <v>0.6781770833333333</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02413803255804047</v>
+        <v>0.02430888099545354</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5854922279792746</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7098445595854922</v>
+        <v>0.7447916666666666</v>
       </c>
     </row>
     <row r="22">
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6714975845410628</v>
+        <v>0.6793203883495147</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02538699586980252</v>
+        <v>0.02702199307548358</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5990338164251208</v>
+        <v>0.616504854368932</v>
       </c>
       <c r="F22" t="n">
-        <v>0.748792270531401</v>
+        <v>0.7330097087378641</v>
       </c>
     </row>
     <row r="23">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6767058823529412</v>
+        <v>0.6911764705882354</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0305704047852903</v>
+        <v>0.02778633959834292</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5941176470588235</v>
+        <v>0.6352941176470588</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="24">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.642295918367347</v>
+        <v>0.6609693877551019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02713245306140219</v>
+        <v>0.02373624867353131</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5663265306122449</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6989795918367347</v>
+        <v>0.7346938775510204</v>
       </c>
     </row>
     <row r="25">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7301932367149759</v>
+        <v>0.6990291262135924</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02488407076475056</v>
+        <v>0.02591753460290525</v>
       </c>
       <c r="E25" t="n">
-        <v>0.642512077294686</v>
+        <v>0.6310679611650486</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7475728155339806</v>
       </c>
     </row>
     <row r="26">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6388829787234043</v>
+        <v>0.6162234042553192</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02644914463670071</v>
+        <v>0.02656214296853158</v>
       </c>
       <c r="E26" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5638297872340425</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6808510638297872</v>
+        <v>0.6914893617021277</v>
       </c>
     </row>
     <row r="27">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.659193548387097</v>
+        <v>0.6843783783783784</v>
       </c>
       <c r="D27" t="n">
-        <v>0.025640908066497</v>
+        <v>0.02471575129790138</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6021505376344086</v>
+        <v>0.6324324324324324</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7204301075268817</v>
+        <v>0.745945945945946</v>
       </c>
     </row>
     <row r="28">
@@ -1037,16 +1037,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6766666666666667</v>
+        <v>0.6589772727272727</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02566958049792829</v>
+        <v>0.02305463273744895</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6045197740112994</v>
+        <v>0.6193181818181818</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7231638418079096</v>
+        <v>0.7329545454545454</v>
       </c>
     </row>
     <row r="29">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.656878612716763</v>
+        <v>0.6763953488372093</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02662891429571913</v>
+        <v>0.02778116460552145</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6127167630057804</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7225433526011561</v>
+        <v>0.7383720930232558</v>
       </c>
     </row>
     <row r="30">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6554802259887005</v>
+        <v>0.6168361581920905</v>
       </c>
       <c r="D30" t="n">
-        <v>0.02829967417333169</v>
+        <v>0.02561331154947515</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5819209039548022</v>
+        <v>0.5423728813559322</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7175141242937854</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="31">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6644117647058825</v>
+        <v>0.678768472906404</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02233270045710625</v>
+        <v>0.02660904674766375</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5931372549019608</v>
+        <v>0.625615763546798</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7107843137254902</v>
+        <v>0.7438423645320197</v>
       </c>
     </row>
   </sheetData>

--- a/intermediate_data/LR_approved_summary.xlsx
+++ b/intermediate_data/LR_approved_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6814576271186441</v>
+        <v>0.6840677966101696</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02073715710883318</v>
+        <v>0.0181495801177503</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6338983050847458</v>
+        <v>0.6406779661016949</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7322033898305085</v>
+        <v>0.7288135593220338</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6548502994011975</v>
+        <v>0.655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02008705755111195</v>
+        <v>0.0201175740762467</v>
       </c>
       <c r="E3" t="n">
-        <v>0.592814371257485</v>
+        <v>0.6077844311377245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6976047904191617</v>
+        <v>0.7155688622754491</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6776265822784809</v>
+        <v>0.6775632911392405</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02022885140028705</v>
+        <v>0.02253847844657896</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6170886075949367</v>
+        <v>0.6234177215189873</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7215189873417721</v>
+        <v>0.7310126582278481</v>
       </c>
     </row>
     <row r="5">
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6524834437086092</v>
+        <v>0.6488741721854305</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01995862350836525</v>
+        <v>0.01985595130492027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6092715231788079</v>
+        <v>0.5993377483443708</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7052980132450332</v>
+        <v>0.695364238410596</v>
       </c>
     </row>
     <row r="6">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6963157894736841</v>
+        <v>0.700032894736842</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0192142400989572</v>
+        <v>0.02107948160712168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6513157894736842</v>
+        <v>0.6348684210526315</v>
       </c>
       <c r="F6" t="n">
         <v>0.7401315789473685</v>
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6479026217228465</v>
+        <v>0.6504868913857679</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02224691587136363</v>
+        <v>0.02033274080427222</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5917602996254682</v>
+        <v>0.599250936329588</v>
       </c>
       <c r="F7" t="n">
         <v>0.700374531835206</v>
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6816666666666669</v>
+        <v>0.6810507246376812</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0242860934991898</v>
+        <v>0.02342131941909679</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.6340579710144928</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7318840579710145</v>
+        <v>0.7463768115942029</v>
       </c>
     </row>
     <row r="9">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6552238805970149</v>
+        <v>0.6568283582089554</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02317210942568256</v>
+        <v>0.02475919724755</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6119402985074627</v>
+        <v>0.5970149253731343</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7052238805970149</v>
+        <v>0.7164179104477612</v>
       </c>
     </row>
     <row r="10">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6759599999999999</v>
+        <v>0.67476</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0216603347391055</v>
+        <v>0.02487752626631741</v>
       </c>
       <c r="E10" t="n">
-        <v>0.604</v>
+        <v>0.612</v>
       </c>
       <c r="F10" t="n">
-        <v>0.724</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="11">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6737446808510638</v>
+        <v>0.6737872340425531</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0255251441699454</v>
+        <v>0.02486572672415388</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5787234042553191</v>
+        <v>0.6042553191489362</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7446808510638298</v>
+        <v>0.7404255319148936</v>
       </c>
     </row>
     <row r="12">
@@ -685,16 +685,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.690219298245614</v>
+        <v>0.695877192982456</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02567032108958861</v>
+        <v>0.02556842340911797</v>
       </c>
       <c r="E12" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6359649122807017</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7543859649122807</v>
+        <v>0.7587719298245614</v>
       </c>
     </row>
     <row r="13">
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6795089285714284</v>
+        <v>0.6825892857142857</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02292470308012953</v>
+        <v>0.02630414261044101</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6116071428571429</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7366071428571429</v>
+        <v>0.7410714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6602950819672131</v>
+        <v>0.662</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01949411646200951</v>
+        <v>0.02199211169854381</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6196721311475409</v>
+        <v>0.6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7049180327868853</v>
+        <v>0.7311475409836066</v>
       </c>
     </row>
     <row r="15">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6553398058252428</v>
+        <v>0.6516990291262136</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0228837146015064</v>
+        <v>0.02494768593855469</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6067961165048543</v>
+        <v>0.5970873786407767</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7184466019417476</v>
+        <v>0.7087378640776699</v>
       </c>
     </row>
     <row r="16">
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6527397260273972</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02447712134752807</v>
+        <v>0.02439955963782123</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5844748858447488</v>
+        <v>0.589041095890411</v>
       </c>
       <c r="F16" t="n">
         <v>0.7123287671232876</v>
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6868036529680366</v>
+        <v>0.6924657534246574</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02466329898942328</v>
+        <v>0.02315962085372267</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6118721461187214</v>
+        <v>0.6210045662100456</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7397260273972602</v>
+        <v>0.7488584474885844</v>
       </c>
     </row>
     <row r="18">
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6798086124401916</v>
+        <v>0.6775119617224883</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02574101771883541</v>
+        <v>0.02631249402698997</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6172248803827751</v>
+        <v>0.6076555023923444</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7607655502392344</v>
       </c>
     </row>
     <row r="19">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6995813953488371</v>
+        <v>0.7017209302325582</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02734613804018465</v>
+        <v>0.02550679964649322</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6372093023255814</v>
+        <v>0.6325581395348837</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7581395348837209</v>
+        <v>0.7534883720930232</v>
       </c>
     </row>
     <row r="20">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6613793103448274</v>
+        <v>0.6611330049261082</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02504620161935741</v>
+        <v>0.02551811742426174</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5911330049261084</v>
+        <v>0.5960591133004927</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7339901477832512</v>
+        <v>0.7241379310344828</v>
       </c>
     </row>
     <row r="21">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6781770833333333</v>
+        <v>0.6821874999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02430888099545354</v>
+        <v>0.03013386269359007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.609375</v>
       </c>
       <c r="F21" t="n">
         <v>0.7447916666666666</v>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6793203883495147</v>
+        <v>0.6862621359223301</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02702199307548358</v>
+        <v>0.02599690147991106</v>
       </c>
       <c r="E22" t="n">
-        <v>0.616504854368932</v>
+        <v>0.6213592233009708</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7330097087378641</v>
+        <v>0.7475728155339806</v>
       </c>
     </row>
     <row r="23">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6911764705882354</v>
+        <v>0.6871764705882353</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02778633959834292</v>
+        <v>0.02782254265835948</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6352941176470588</v>
+        <v>0.6294117647058823</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7705882352941177</v>
       </c>
     </row>
     <row r="24">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6609693877551019</v>
+        <v>0.655204081632653</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02373624867353131</v>
+        <v>0.02638850831859363</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.7397959183673469</v>
       </c>
     </row>
     <row r="25">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6990291262135924</v>
+        <v>0.6967475728155341</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02591753460290525</v>
+        <v>0.02627739503046623</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6310679611650486</v>
+        <v>0.6359223300970874</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7475728155339806</v>
+        <v>0.8009708737864077</v>
       </c>
     </row>
     <row r="26">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6162234042553192</v>
+        <v>0.617872340425532</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02656214296853158</v>
+        <v>0.02732944551353733</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5638297872340425</v>
+        <v>0.5531914893617021</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6914893617021277</v>
+        <v>0.675531914893617</v>
       </c>
     </row>
     <row r="27">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.6843783783783784</v>
+        <v>0.687135135135135</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02471575129790138</v>
+        <v>0.0268053150162334</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6324324324324324</v>
+        <v>0.6162162162162163</v>
       </c>
       <c r="F27" t="n">
-        <v>0.745945945945946</v>
+        <v>0.7405405405405405</v>
       </c>
     </row>
     <row r="28">
@@ -1037,16 +1037,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6589772727272727</v>
+        <v>0.6586931818181818</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02305463273744895</v>
+        <v>0.02226713669740439</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6193181818181818</v>
+        <v>0.6079545454545454</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7329545454545454</v>
+        <v>0.7102272727272727</v>
       </c>
     </row>
     <row r="29">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.6763953488372093</v>
+        <v>0.673546511627907</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02778116460552145</v>
+        <v>0.02621494032599669</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.5872093023255814</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7383720930232558</v>
+        <v>0.7267441860465116</v>
       </c>
     </row>
     <row r="30">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6168361581920905</v>
+        <v>0.6149152542372881</v>
       </c>
       <c r="D30" t="n">
-        <v>0.02561331154947515</v>
+        <v>0.0269186446496621</v>
       </c>
       <c r="E30" t="n">
         <v>0.5423728813559322</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6779661016949152</v>
       </c>
     </row>
     <row r="31">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.678768472906404</v>
+        <v>0.6807881773399014</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02660904674766375</v>
+        <v>0.02854413405615825</v>
       </c>
       <c r="E31" t="n">
-        <v>0.625615763546798</v>
+        <v>0.5911330049261084</v>
       </c>
       <c r="F31" t="n">
         <v>0.7438423645320197</v>
